--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>1/9</t>
         </is>
       </c>
     </row>
@@ -723,22 +731,22 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -771,12 +779,12 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +798,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +842,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +852,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +909,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -926,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +945,1018 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -862,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,17 +923,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -939,13 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -983,24 +991,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1010,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1164,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1175,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1211,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1236,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1260,17 +1272,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1280,13 +1292,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1397,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1507,12 +1523,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1589,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1623,7 +1639,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1734,7 +1750,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1839,13 +1855,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1956,7 +1976,455 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -991,24 +991,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1221,24 +1221,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,17 +1391,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1407,13 +1411,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1528,7 +1536,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1639,7 +1647,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1750,7 +1758,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1819,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1865,7 +1873,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1976,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2086,12 +2094,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2160,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2202,7 +2210,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2271,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2313,7 +2321,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2382,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2424,7 +2432,233 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1330,36 +1330,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1367,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1391,37 +1387,33 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1441,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1482,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,37 +1502,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1636,7 +1632,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1647,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1675,32 +1671,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1732,33 +1732,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1786,32 +1790,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1819,7 +1827,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1843,37 +1851,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1973,7 +1981,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1984,7 +1992,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2099,7 +2107,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2168,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2210,7 +2218,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2279,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2321,7 +2329,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2432,7 +2440,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2501,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2543,7 +2551,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2612,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2658,7 +2666,907 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A50759D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,13 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1478,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1517,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1593,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1708,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1800,24 +1804,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1827,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1876,12 +1880,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1909,32 +1913,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1942,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1966,17 +1974,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1986,13 +1994,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2092,7 +2104,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2135,32 +2147,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -2168,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2192,33 +2208,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2246,32 +2266,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -2279,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2303,33 +2327,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,7 +2529,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2540,7 +2568,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2612,7 +2640,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2651,7 +2679,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2727,7 +2755,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2766,7 +2794,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2805,32 +2833,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:33</t>
@@ -2838,7 +2870,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2862,33 +2894,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2985,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,7 +3096,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3099,7 +3135,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3175,7 +3211,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,7 +3322,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3330,13 +3366,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3437,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3459,22 +3499,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3507,12 +3547,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3526,47 +3566,959 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>3/14</t>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A50759D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,13 +1641,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,7 +1755,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1766,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,17 +1874,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1950,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1989,22 +1993,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,17 +2113,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,7 +2227,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2238,7 +2242,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,14 +2346,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -2357,7 +2361,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2568,7 +2572,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2640,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2755,7 +2759,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2870,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2924,7 +2928,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3024,7 +3028,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3063,32 +3067,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3096,7 +3104,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3120,17 +3128,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3140,12 +3148,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3178,32 +3186,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3211,7 +3223,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3235,17 +3247,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3255,13 +3267,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3289,32 +3305,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3322,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3346,37 +3366,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3476,7 +3496,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3491,7 +3511,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3519,32 +3539,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3552,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3576,17 +3600,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3596,17 +3620,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3634,32 +3658,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3667,7 +3695,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3691,32 +3719,32 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3749,32 +3777,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -3782,7 +3814,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3806,29 +3838,29 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -3836,7 +3868,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3929,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3936,7 +3968,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3951,7 +3983,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4044,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4127,7 +4159,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4181,7 +4213,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4274,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4281,7 +4313,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4353,7 +4385,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4397,12 +4429,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4468,7 +4500,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4522,6 +4554,803 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,18 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1526,17 +1530,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1655,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,17 +1764,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1893,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,7 +1997,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2008,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2232,17 +2236,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2361,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2465,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2472,7 +2476,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2577,13 +2581,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,17 +2696,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2798,18 +2806,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2913,22 +2925,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3028,18 +3040,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3148,17 +3164,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3293,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3381,7 +3397,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3396,7 +3412,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3501,17 +3517,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3646,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3749,7 +3765,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3815,12 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3814,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3868,7 +3884,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3896,32 +3912,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -3929,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3953,17 +3973,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3973,17 +3993,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4011,32 +4031,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4044,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4068,17 +4092,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4088,17 +4112,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4126,32 +4150,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:33</t>
@@ -4159,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4183,37 +4211,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4241,32 +4269,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -4274,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4298,17 +4330,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4318,13 +4350,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4352,32 +4388,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4385,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4409,17 +4449,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4429,17 +4469,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4467,32 +4507,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -4500,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4524,33 +4568,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4578,32 +4626,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -4611,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4635,17 +4687,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4655,17 +4707,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4780,7 +4832,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4808,32 +4860,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4841,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4865,33 +4921,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4952,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4996,17 +5056,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5127,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5106,7 +5166,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5121,7 +5181,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5242,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5226,13 +5286,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5357,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5347,7 +5411,689 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A50759D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55702D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,17 +1883,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,14 +2350,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,17 +2581,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3755,17 +3755,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4350,17 +4350,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4745,32 +4745,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4778,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4802,17 +4806,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4822,17 +4826,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5012,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5066,7 +5070,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5094,32 +5098,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5127,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5151,17 +5159,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5171,17 +5179,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5209,32 +5217,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -5242,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5266,17 +5278,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5286,17 +5298,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5324,32 +5336,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -5357,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5381,29 +5397,29 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -5411,7 +5427,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5526,7 +5542,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5626,7 +5642,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5641,7 +5657,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5833,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,7 +5944,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5972,17 +5988,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6097,6 +6113,466 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A50759D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2811,17 +2811,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,17 +4588,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5346,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5455,32 +5455,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -5488,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5512,17 +5516,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5532,17 +5536,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5570,32 +5574,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>08:33</t>
@@ -5603,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5627,17 +5635,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5647,12 +5655,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5718,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5833,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5872,7 +5880,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5944,7 +5952,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5998,7 +6006,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6067,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6098,7 +6106,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6170,7 +6178,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6219,7 +6227,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6285,7 +6293,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,7 +6408,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6444,12 +6452,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6515,7 +6523,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6569,7 +6577,344 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55702D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,22 +1997,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,22 +5174,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5417,12 +5417,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5584,19 +5584,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5660,12 +5660,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5808,32 +5808,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -5841,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5865,17 +5869,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5885,13 +5889,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5919,32 +5927,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5952,7 +5964,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5976,37 +5988,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6145,32 +6157,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -6178,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6202,17 +6218,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6222,12 +6238,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6293,7 +6309,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6332,7 +6348,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6347,7 +6363,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6424,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6457,12 +6473,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6539,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6577,7 +6593,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6654,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6753,7 +6769,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6797,13 +6813,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6811,22 +6831,22 @@
       <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6859,12 +6879,12 @@
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6878,43 +6898,388 @@
       <c r="T55" s="2" t="inlineStr"/>
       <c r="U55" s="2" t="inlineStr">
         <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
           <t>14:55</t>
         </is>
       </c>
-      <c r="V55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W55" s="2" t="inlineStr">
+      <c r="W56" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X55" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z55" s="2" t="inlineStr">
+      <c r="Z56" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
+      <c r="AA56" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr"/>
-      <c r="AC55" s="2" t="inlineStr">
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
         <is>
           <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1640,22 +1640,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2930,17 +2930,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,17 +5655,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5889,17 +5889,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5937,24 +5937,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6276,32 +6276,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6309,7 +6313,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6333,17 +6337,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6353,12 +6357,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6391,32 +6395,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>08:33</t>
@@ -6424,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6448,17 +6456,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6468,17 +6476,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6506,32 +6514,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6539,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6563,37 +6575,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6666,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6693,7 +6705,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6736,32 +6748,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -6769,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6793,17 +6809,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6813,17 +6829,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6900,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6923,7 +6939,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6999,7 +7015,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,7 +7126,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7159,12 +7175,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7172,22 +7188,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7220,12 +7236,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7239,47 +7255,852 @@
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>14/15</t>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,18 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1411,12 +1415,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,14 +1529,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -1540,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1764,17 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2012,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,12 +2121,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,12 +2235,12 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2426,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,18 +2469,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2584,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2591,7 +2599,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2706,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2814,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2886,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,14 +2933,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>81.8</t>
@@ -2940,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3045,12 +3053,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3120,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3159,14 +3167,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -3174,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3358,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3397,7 +3405,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3412,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3517,17 +3525,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3636,12 +3644,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3711,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3750,7 +3758,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3830,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3949,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3988,12 +3996,12 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4068,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4122,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4226,14 +4234,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>81.8</t>
@@ -4241,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4353,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4360,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4464,14 +4472,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -4479,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,7 +4591,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4663,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4707,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4821,7 +4829,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4901,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4945,12 +4953,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5016,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5055,12 +5063,12 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5135,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,7 +5182,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5189,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5293,7 +5301,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5308,7 +5316,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5492,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5531,7 +5539,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5611,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5650,14 +5658,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>81.8</t>
@@ -5665,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5770,12 +5778,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5845,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5884,22 +5892,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6003,7 +6011,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6018,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6118,18 +6126,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6313,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6357,12 +6369,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6432,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6471,14 +6483,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>81.8</t>
@@ -6486,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6633,32 +6645,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6666,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6690,17 +6706,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6710,17 +6726,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6758,24 +6774,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6785,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6824,22 +6840,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6867,32 +6883,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6900,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6924,17 +6944,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6944,12 +6964,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -6982,32 +7002,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7015,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7039,33 +7063,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7165,7 +7193,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7180,7 +7208,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7208,32 +7236,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -7241,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7265,27 +7297,27 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7323,32 +7355,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7356,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7380,17 +7416,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7400,12 +7436,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7471,7 +7507,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7510,7 +7546,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7525,7 +7561,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7701,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7816,7 +7852,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7870,7 +7906,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7967,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7975,17 +8011,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7993,22 +8029,22 @@
       <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A50759D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8041,12 +8077,12 @@
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8060,47 +8096,1082 @@
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W65" s="2" t="inlineStr">
+      <c r="W67" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X65" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y65" s="2" t="inlineStr">
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z65" s="2" t="inlineStr">
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A55702D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>1/15</t>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,22 +2699,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3048,22 +3048,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,22 +3286,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,22 +3520,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,22 +3877,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,22 +4115,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,22 +4948,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5420,22 +5420,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5773,22 +5773,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6245,22 +6245,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6602,22 +6602,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6721,22 +6721,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7474,32 +7474,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -7507,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7531,17 +7535,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7551,12 +7555,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7589,32 +7593,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -7622,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7646,37 +7654,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7704,32 +7712,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7737,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7761,37 +7773,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7819,32 +7831,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7852,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7876,37 +7892,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7934,32 +7950,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7967,7 +7987,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7991,37 +8011,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8121,7 +8141,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8136,7 +8156,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8217,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8236,7 +8256,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8251,7 +8271,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8279,32 +8299,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8312,7 +8336,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8336,37 +8360,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8451,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8481,7 +8505,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8566,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8596,7 +8620,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8681,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8772,7 +8796,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8826,7 +8850,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8911,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8936,12 +8960,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9026,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9117,7 +9141,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9161,17 +9185,937 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A50759D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>81.5</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>5/15</t>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,17 +2469,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3167,22 +3167,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,22 +3405,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,17 +3639,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,17 +4353,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,22 +4472,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4829,22 +4829,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,22 +5063,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5182,22 +5182,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5301,17 +5301,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6011,22 +6011,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6126,17 +6126,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6364,17 +6364,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7078,17 +7078,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7193,22 +7193,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7312,22 +7312,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7431,17 +7431,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7550,17 +7550,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -8418,32 +8418,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -8451,7 +8455,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8475,27 +8479,27 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8533,32 +8537,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8566,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8590,37 +8598,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8648,32 +8656,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8681,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8705,37 +8717,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8763,32 +8775,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8796,7 +8812,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8820,37 +8836,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8878,32 +8894,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -8911,7 +8931,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8935,37 +8955,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8993,32 +9013,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9026,7 +9050,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9050,32 +9074,32 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9108,32 +9132,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -9141,7 +9169,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9165,32 +9193,32 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9256,7 +9284,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9295,7 +9323,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9310,7 +9338,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9338,32 +9366,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9371,7 +9403,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9395,32 +9427,32 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9486,7 +9518,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9540,7 +9572,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9633,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9640,7 +9672,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9716,7 +9748,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9831,7 +9863,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9885,7 +9917,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10008,22 +10040,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55702D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10056,12 +10088,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10075,47 +10107,1197 @@
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr">
         <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="V82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr">
+      <c r="W83" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
+      <c r="AB84" s="2" t="inlineStr">
         <is>
           <t>80.3</t>
         </is>
       </c>
-      <c r="AC82" s="2" t="inlineStr">
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
         <is>
           <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,22 +2933,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4234,22 +4234,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4829,17 +4829,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4953,17 +4953,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5658,22 +5658,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,17 +5778,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6483,22 +6483,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,17 +6607,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,17 +6964,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7793,17 +7793,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8499,17 +8499,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8613,17 +8613,17 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9376,24 +9376,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9600,32 +9600,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9633,7 +9637,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9657,17 +9661,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9677,17 +9681,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9715,32 +9719,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>08:33</t>
@@ -9748,7 +9756,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9772,37 +9780,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9830,32 +9838,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -9863,7 +9875,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9887,17 +9899,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9907,7 +9919,7 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -9917,7 +9929,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9990,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10017,7 +10029,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10060,32 +10072,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -10093,7 +10109,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10117,17 +10133,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10137,17 +10153,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10175,32 +10191,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10208,7 +10228,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10232,32 +10252,32 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10290,32 +10310,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10323,7 +10347,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10347,17 +10371,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10367,17 +10391,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10462,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10492,7 +10516,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10577,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10607,7 +10631,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10692,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10707,7 +10731,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10783,7 +10807,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10898,7 +10922,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11013,7 +11037,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11062,7 +11086,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11128,7 +11152,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11190,22 +11214,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11238,12 +11262,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11292,12 +11316,587 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A50759D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3167,22 +3167,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,22 +4472,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8851,22 +8851,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10201,24 +10201,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10429,32 +10429,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10462,7 +10466,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10486,37 +10490,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10635,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10696,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10807,7 +10811,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10922,7 +10926,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10961,7 +10965,7 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -10976,7 +10980,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11041,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11152,7 +11156,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11267,7 +11271,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11321,7 +11325,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11386,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11436,7 +11440,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11497,7 +11501,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11612,7 +11616,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11661,7 +11665,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11727,7 +11731,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11789,22 +11793,22 @@
       <c r="A97" s="2" t="inlineStr"/>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -11837,12 +11841,12 @@
       <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11856,47 +11860,277 @@
       <c r="T97" s="2" t="inlineStr"/>
       <c r="U97" s="2" t="inlineStr">
         <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
           <t>20:10</t>
         </is>
       </c>
-      <c r="V97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W97" s="2" t="inlineStr">
+      <c r="W98" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X97" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y97" s="2" t="inlineStr">
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z97" s="2" t="inlineStr">
+      <c r="Z98" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA97" s="2" t="inlineStr">
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB97" s="2" t="inlineStr">
+      <c r="AB98" s="2" t="inlineStr">
         <is>
           <t>84.5</t>
         </is>
       </c>
-      <c r="AC97" s="2" t="inlineStr">
+      <c r="AC98" s="2" t="inlineStr">
         <is>
           <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3882,17 +3882,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,17 +4358,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,17 +5425,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,17 +6250,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,17 +6607,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7555,17 +7555,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,17 +7674,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7793,17 +7793,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9213,17 +9213,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9562,12 +9562,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,17 +9681,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10439,24 +10439,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10663,32 +10663,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -10696,7 +10700,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10720,17 +10724,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10740,12 +10744,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10811,7 +10815,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10893,32 +10897,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -10926,7 +10934,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10950,17 +10958,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10970,17 +10978,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11008,32 +11016,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11041,7 +11053,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11065,17 +11077,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11085,12 +11097,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11123,32 +11135,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -11156,7 +11172,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11180,17 +11196,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11200,17 +11216,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -11238,32 +11254,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11271,7 +11291,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11295,17 +11315,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11315,12 +11335,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11353,32 +11373,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11386,7 +11410,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11410,17 +11434,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11430,17 +11454,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11525,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11555,7 +11579,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11640,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11731,7 +11755,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11785,7 +11809,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11870,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11895,12 +11919,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11908,22 +11932,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11956,12 +11980,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11975,7 +11999,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12005,17 +12029,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -12023,22 +12047,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A55702D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12071,12 +12095,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12090,47 +12114,507 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>84.4</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A55702D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>81.5</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>4/15</t>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东78路.xlsx
+++ b/data/export/2026-10-25-浦东78路.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,17 +2819,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,17 +4358,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,17 +6726,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7555,17 +7555,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8031,17 +8031,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8261,17 +8261,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9213,17 +9213,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9919,17 +9919,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10034,17 +10034,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10978,17 +10978,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11492,32 +11492,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>08:33</t>
@@ -11525,7 +11529,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11549,17 +11553,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11569,7 +11573,7 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -11579,7 +11583,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11698,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -11722,32 +11726,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11755,7 +11763,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11779,17 +11787,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11799,17 +11807,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11952,32 +11960,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -11985,7 +11997,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12009,17 +12021,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12029,17 +12041,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12112,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12154,7 +12166,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12194,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -12215,7 +12231,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12239,17 +12255,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12259,12 +12275,12 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12297,32 +12313,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -12330,7 +12350,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12354,17 +12374,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12374,17 +12394,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -12445,7 +12465,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12489,17 +12509,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12580,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12614,7 +12634,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
